--- a/Data/Parameters.xlsx
+++ b/Data/Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.dagostino\Desktop\PhD_local\Experience1\Codes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdagostino\Desktop\GITHUB\TRoot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4931072B-8466-4163-8FD5-40E1BF8DBDFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FCB987-A69E-4354-A0F1-7F627F05C8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="117">
   <si>
     <t>Name/Tissue</t>
   </si>
@@ -313,19 +313,100 @@
   </si>
   <si>
     <t>Aerenchyma*</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>secondary growth</t>
+  </si>
+  <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>randomness</t>
+  </si>
+  <si>
+    <t>plant type</t>
+  </si>
+  <si>
+    <t>aerenchyma</t>
+  </si>
+  <si>
+    <t>proportion</t>
+  </si>
+  <si>
+    <t>n_files</t>
+  </si>
+  <si>
+    <t>xylem</t>
+  </si>
+  <si>
+    <t>max_size</t>
+  </si>
+  <si>
+    <t>cell_diameter</t>
+  </si>
+  <si>
+    <t>n_cells</t>
+  </si>
+  <si>
+    <t>stele</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>layer_diameter</t>
+  </si>
+  <si>
+    <t>phloem</t>
+  </si>
+  <si>
+    <t>n_layers</t>
+  </si>
+  <si>
+    <t>pericycle</t>
+  </si>
+  <si>
+    <t>endodermis</t>
+  </si>
+  <si>
+    <t>cortex</t>
+  </si>
+  <si>
+    <t>exodermis</t>
+  </si>
+  <si>
+    <t>epidermis</t>
+  </si>
+  <si>
+    <t>param_id</t>
+  </si>
+  <si>
+    <t>stele_SD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -348,8 +429,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -630,375 +714,477 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="28.140625" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
     <col min="3" max="3" width="69.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="str">
+        <f>CONCATENATE(B2,"_",C2)</f>
+        <v>secondary growth_parameter</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <f t="shared" ref="A3:A26" si="0">CONCATENATE(B3,"_",C3)</f>
+        <v>randomness_parameter</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <f t="shared" si="0"/>
+        <v>plant type_parameter</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>aerenchyma_proportion</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>aerenchyma_n_files</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>xylem_max_size</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <f t="shared" si="0"/>
+        <v>xylem_cell_diameter</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f t="shared" si="0"/>
+        <v>xylem_n_files</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f t="shared" si="0"/>
+        <v>xylem_n_cells</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <f t="shared" si="0"/>
+        <v>stele_cell_diameter</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
         <v>28</v>
       </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" t="s">
         <v>30</v>
       </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f t="shared" si="0"/>
+        <v>stele_layer_diameter</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" t="s">
         <v>32</v>
       </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f t="shared" si="0"/>
+        <v>phloem_n_layers</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
         <v>35</v>
       </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f t="shared" si="0"/>
+        <v>phloem_cell_diameter</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
         <v>36</v>
       </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f t="shared" si="0"/>
+        <v>phloem_proportion</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
         <v>37</v>
       </c>
-      <c r="D16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="E16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f t="shared" si="0"/>
+        <v>pericycle_cell_diameter</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="E17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <f t="shared" si="0"/>
+        <v>pericycle_n_layers</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" t="s">
         <v>40</v>
       </c>
-      <c r="D18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="E18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <f t="shared" si="0"/>
+        <v>endodermis_cell_diameter</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
         <v>42</v>
       </c>
-      <c r="D19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <f t="shared" si="0"/>
+        <v>endodermis_n_layers</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
         <v>43</v>
       </c>
-      <c r="D20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="E20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f t="shared" si="0"/>
+        <v>cortex_cell_diameter</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" t="s">
         <v>45</v>
       </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="E21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f t="shared" si="0"/>
+        <v>cortex_n_layers</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
         <v>46</v>
       </c>
-      <c r="D22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="E22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f t="shared" si="0"/>
+        <v>exodermis_cell_diameter</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
         <v>48</v>
       </c>
-      <c r="D23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f t="shared" si="0"/>
+        <v>exodermis_n_layers</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
         <v>49</v>
       </c>
-      <c r="D24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="E24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f t="shared" si="0"/>
+        <v>epidermis_cell_diameter</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" t="s">
         <v>51</v>
       </c>
-      <c r="D25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="str">
+        <f t="shared" si="0"/>
+        <v>epidermis_n_layers</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" t="s">
         <v>52</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>53</v>
       </c>
     </row>

--- a/Data/Parameters.xlsx
+++ b/Data/Parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdagostino\Desktop\GITHUB\TRoot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FCB987-A69E-4354-A0F1-7F627F05C8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969E0F83-8870-478B-84FC-05B482DFA4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -720,6 +720,7 @@
     <col min="1" max="1" width="28.140625" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
     <col min="3" max="3" width="69.42578125" customWidth="1"/>
+    <col min="4" max="4" width="59.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
